--- a/p6_deployment/data/spain/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,392 +465,1263 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDmOFmNG</t>
+          <t>hO0nKEm3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45438.66666666666</v>
+        <v>45519.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i   esp </t>
+          <t xml:space="preserve">garcia v 
+  esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan  sevilla </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42714</v>
+        <v>53331</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>148</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>26.47525252525253</v>
+      </c>
+      <c r="O2" t="n">
+        <v>182.3277777777778</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.674579124579125</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>79.48888888888888</v>
+      </c>
+      <c r="R2" t="n">
+        <v>23390067.34006734</v>
+      </c>
+      <c r="S2" t="n">
+        <v>82.10353535353535</v>
+      </c>
+      <c r="T2" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>183.7291666666667</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>76.29166666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12690625</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>79.04166666666667</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>26.80696046534556</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>182.3584048111998</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.482798481711525</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>75.63595090209995</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12224777.43271221</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>79.33664349797891</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>24.6952947845805</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>184.4520975056689</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.136337868480725</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>71.09452947845806</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>5351535.572562358</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>76.36493764172336</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>148</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>27.675</v>
+      </c>
+      <c r="O3" t="n">
+        <v>182</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>11397500</v>
+      </c>
+      <c r="S3" t="n">
+        <v>78.925</v>
+      </c>
+      <c r="T3" t="n">
+        <v>25.39523809523809</v>
+      </c>
+      <c r="U3" t="n">
+        <v>181.1253968253968</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.465079365079365</v>
+      </c>
+      <c r="W3" t="n">
+        <v>79.83333333333334</v>
+      </c>
+      <c r="X3" t="n">
+        <v>26777777.77777778</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>82.89999999999999</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>27.8742420044941</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>183.6039615846339</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.980952380952381</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>75.96662049435159</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10732663.21913381</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>79.16251731461814</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>24.26983254840398</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>178.1160474446189</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.135478806907378</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>74.90235478806908</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>15969123.49555207</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>80.56597767312053</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>A7v4ruhp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>148</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>27.11666666666666</v>
+      </c>
+      <c r="O4" t="n">
+        <v>182.1888888888889</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>75.16944444444445</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8280000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>78.31666666666666</v>
+      </c>
+      <c r="T4" t="n">
+        <v>24.0625</v>
+      </c>
+      <c r="U4" t="n">
+        <v>180.71875</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>71.46875</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3939843.75</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>76.40625</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>25.82315592903828</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>179.4782913165266</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.2562558356676</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>74.53842203548086</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>7604421.101774042</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>77.49913632119514</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>23.63474607234198</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>180.9953076882927</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>70.7673225812064</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4134698.633076419</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>76.27805441016986</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>h8oAv4Ts</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H5" t="n">
+        <v>148</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>25.01587301587302</v>
+      </c>
+      <c r="O5" t="n">
+        <v>180.3829365079365</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.035714285714286</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>74.29960317460316</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8950000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>78.18650793650794</v>
+      </c>
+      <c r="T5" t="n">
+        <v>25.92129629629629</v>
+      </c>
+      <c r="U5" t="n">
+        <v>186.5416666666667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.657407407407407</v>
+      </c>
+      <c r="W5" t="n">
+        <v>76.48611111111111</v>
+      </c>
+      <c r="X5" t="n">
+        <v>15328935.18518518</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>79.9375</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>26.77285236502627</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>178.975347985348</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.104925147316452</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>72.64460742156395</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4917440.476190476</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>74.56647077560122</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>24.38625265895832</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>183.9209228428213</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.5843737494998</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>75.43027026600114</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>12577507.92422232</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>80.75036356647922</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alvendiz l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>148</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>26.13690476190476</v>
+      </c>
+      <c r="U6" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>69.40873015873015</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1997470.238095238</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>73.11706349206349</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>26.35643166357452</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>183.8209029066172</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.05741341991342</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>72.52097247990106</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6964055.156153371</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>75.95047928262214</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>27.45431225121627</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>181.4008452503808</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>69.11993709764607</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1765501.867413632</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>72.33573639982309</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Qkg2vOrk</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>AD5WKzFn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H7" t="n">
+        <v>148</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>182.875</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="R7" t="n">
+        <v>12662500</v>
+      </c>
+      <c r="S7" t="n">
+        <v>80.375</v>
+      </c>
+      <c r="T7" t="n">
+        <v>26.16666666666666</v>
+      </c>
+      <c r="U7" t="n">
+        <v>181.4222222222222</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.805555555555556</v>
+      </c>
+      <c r="W7" t="n">
+        <v>81.90555555555555</v>
+      </c>
+      <c r="X7" t="n">
+        <v>46715833.33333333</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>85.94444444444444</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>24.33493666697448</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>180.1266652814972</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.119127651060424</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>72.60331517222274</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>6507113.345338136</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>76.89876873826454</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>23.84827369544309</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>180.441840069361</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.337283509895186</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>79.6264388211425</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>38270092.80905344</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>85.24200645170349</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
       </c>
-      <c r="J2" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45522.58333333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>148</v>
       </c>
-      <c r="K2" t="n">
+      <c r="I8" t="n">
         <v>1481</v>
       </c>
-      <c r="L2" t="n">
+      <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="N2" t="n">
-        <v>24.77777777777778</v>
-      </c>
-      <c r="O2" t="n">
-        <v>187</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.444444444444444</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>75.66666666666667</v>
-      </c>
-      <c r="R2" t="n">
-        <v>13711111.11111111</v>
-      </c>
-      <c r="S2" t="n">
-        <v>80</v>
-      </c>
-      <c r="T2" t="n">
-        <v>26.375</v>
-      </c>
-      <c r="U2" t="n">
-        <v>181.75</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W2" t="n">
-        <v>82.625</v>
-      </c>
-      <c r="X2" t="n">
-        <v>50237500</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>183.375</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>73</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8700000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>80.25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.142857142857143</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>77.28571428571429</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>25757142.85714286</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>84</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>311</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>61700000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>321</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>177</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>172000000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>180</v>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>25.81139971139971</v>
+      </c>
+      <c r="O8" t="n">
+        <v>181.7988455988456</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.703318903318903</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>79.01890331890331</v>
+      </c>
+      <c r="R8" t="n">
+        <v>24489610.38961039</v>
+      </c>
+      <c r="S8" t="n">
+        <v>82.08124098124098</v>
+      </c>
+      <c r="T8" t="n">
+        <v>29.24682539682539</v>
+      </c>
+      <c r="U8" t="n">
+        <v>179.8547619047619</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.392857142857143</v>
+      </c>
+      <c r="W8" t="n">
+        <v>75.71904761904761</v>
+      </c>
+      <c r="X8" t="n">
+        <v>7734007.936507936</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>76.87619047619049</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>24.39047686268183</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>180.9509531875992</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.600210938130193</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>75.17326638165149</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15709285.8789761</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>80.11120513027345</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>28.82970790424207</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>179.8954182463499</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.419048515321807</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>74.12472103465893</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>6178234.653545211</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>75.34734209889488</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45522.6875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>148</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>28.55787037037037</v>
+      </c>
+      <c r="O9" t="n">
+        <v>182.9606481481482</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.349537037037037</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>76.37037037037038</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10193981.48148148</v>
+      </c>
+      <c r="S9" t="n">
+        <v>77.4375</v>
+      </c>
+      <c r="T9" t="n">
+        <v>25.73333333333333</v>
+      </c>
+      <c r="U9" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.366666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>85.93333333333332</v>
+      </c>
+      <c r="X9" t="n">
+        <v>79483333.33333333</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>88.86666666666667</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>27.46533098226462</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>180.9545636158909</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.132863449797088</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>74.77383742624018</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>8073784.675786965</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>76.72069171611506</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>25.68593355020821</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>181.0941356299605</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.869857963428287</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>84.44514330698541</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>65112391.2284212</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>87.83036277938974</v>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/spain/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM9"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,130 +495,135 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>id_team_home_rival_team</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -680,84 +685,85 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>26.47525252525253</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>182.3277777777778</v>
+        <v>26.37732884399551</v>
       </c>
       <c r="P2" t="n">
-        <v>1.674579124579125</v>
+        <v>182.8641975308642</v>
       </c>
       <c r="Q2" t="n">
-        <v>79.48888888888888</v>
+        <v>1.597867564534231</v>
       </c>
       <c r="R2" t="n">
-        <v>23390067.34006734</v>
+        <v>79.41111111111111</v>
       </c>
       <c r="S2" t="n">
-        <v>82.10353535353535</v>
+        <v>23003254.76992144</v>
       </c>
       <c r="T2" t="n">
-        <v>26.58333333333333</v>
+        <v>82.17519640852974</v>
       </c>
       <c r="U2" t="n">
-        <v>183.7291666666667</v>
+        <v>26.66071428571428</v>
       </c>
       <c r="V2" t="n">
-        <v>1.333333333333333</v>
+        <v>183.6785714285714</v>
       </c>
       <c r="W2" t="n">
-        <v>76.29166666666667</v>
+        <v>1.339285714285714</v>
       </c>
       <c r="X2" t="n">
-        <v>12690625</v>
+        <v>76.46428571428571</v>
       </c>
       <c r="Y2" t="n">
-        <v>79.04166666666667</v>
+        <v>12815178.57142857</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.80696046534556</v>
+        <v>79.125</v>
       </c>
       <c r="AA2" t="n">
-        <v>182.3584048111998</v>
+        <v>27.13197486469797</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.482798481711525</v>
+        <v>181.8494231956703</v>
       </c>
       <c r="AC2" t="n">
-        <v>75.63595090209995</v>
+        <v>1.509932348988413</v>
       </c>
       <c r="AD2" t="n">
-        <v>12224777.43271221</v>
+        <v>76.35683611201918</v>
       </c>
       <c r="AE2" t="n">
-        <v>79.33664349797891</v>
+        <v>13462277.18753405</v>
       </c>
       <c r="AF2" t="n">
-        <v>24.6952947845805</v>
+        <v>79.53628246340489</v>
       </c>
       <c r="AG2" t="n">
-        <v>184.4520975056689</v>
+        <v>24.82088293650794</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.136337868480725</v>
+        <v>184.5580853174603</v>
       </c>
       <c r="AI2" t="n">
-        <v>71.09452947845806</v>
+        <v>1.131795634920635</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5351535.572562358</v>
+        <v>70.98271329365079</v>
       </c>
       <c r="AK2" t="n">
-        <v>76.36493764172336</v>
-      </c>
-      <c r="AL2" t="inlineStr">
+        <v>5247843.625992063</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>76.04432043650795</v>
+      </c>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0Q3vjDhH</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>p2dFnNso</t>
         </is>
@@ -819,84 +825,85 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>27.675</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>182</v>
+        <v>27.60416666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>182.1875</v>
       </c>
       <c r="Q3" t="n">
-        <v>76.3</v>
+        <v>1.854166666666667</v>
       </c>
       <c r="R3" t="n">
-        <v>11397500</v>
+        <v>76.33333333333333</v>
       </c>
       <c r="S3" t="n">
-        <v>78.925</v>
+        <v>11460416.66666667</v>
       </c>
       <c r="T3" t="n">
-        <v>25.39523809523809</v>
+        <v>78.95833333333333</v>
       </c>
       <c r="U3" t="n">
-        <v>181.1253968253968</v>
+        <v>25.24583333333333</v>
       </c>
       <c r="V3" t="n">
-        <v>1.465079365079365</v>
+        <v>181.1972222222222</v>
       </c>
       <c r="W3" t="n">
-        <v>79.83333333333334</v>
+        <v>1.456944444444445</v>
       </c>
       <c r="X3" t="n">
-        <v>26777777.77777778</v>
+        <v>79.66666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>82.89999999999999</v>
+        <v>26460555.55555556</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.8742420044941</v>
+        <v>82.91249999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>183.6039615846339</v>
+        <v>28.11496175393234</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.980952380952381</v>
+        <v>183.2451330532213</v>
       </c>
       <c r="AC3" t="n">
-        <v>75.96662049435159</v>
+        <v>2.024999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>10732663.21913381</v>
+        <v>76.09579293255764</v>
       </c>
       <c r="AE3" t="n">
-        <v>79.16251731461814</v>
+        <v>10877746.98340875</v>
       </c>
       <c r="AF3" t="n">
-        <v>24.26983254840398</v>
+        <v>79.10886931695754</v>
       </c>
       <c r="AG3" t="n">
-        <v>178.1160474446189</v>
+        <v>24.46636663774822</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.135478806907378</v>
+        <v>178.3515415140415</v>
       </c>
       <c r="AI3" t="n">
-        <v>74.90235478806908</v>
+        <v>1.138280798149219</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15969123.49555207</v>
+        <v>74.84877096587624</v>
       </c>
       <c r="AK3" t="n">
-        <v>80.56597767312053</v>
-      </c>
-      <c r="AL3" t="inlineStr">
+        <v>15307687.00597648</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>80.46891467450678</v>
+      </c>
+      <c r="AM3" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>A7v4ruhp</t>
         </is>
@@ -958,84 +965,85 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>27.11666666666666</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>182.1888888888889</v>
+        <v>27.24305555555555</v>
       </c>
       <c r="P4" t="n">
-        <v>1.416666666666667</v>
+        <v>182.0532407407408</v>
       </c>
       <c r="Q4" t="n">
-        <v>75.16944444444445</v>
+        <v>1.451388888888889</v>
       </c>
       <c r="R4" t="n">
-        <v>8280000</v>
+        <v>75.18287037037037</v>
       </c>
       <c r="S4" t="n">
-        <v>78.31666666666666</v>
+        <v>8295833.333333333</v>
       </c>
       <c r="T4" t="n">
-        <v>24.0625</v>
+        <v>78.24305555555556</v>
       </c>
       <c r="U4" t="n">
-        <v>180.71875</v>
+        <v>24.14583333333333</v>
       </c>
       <c r="V4" t="n">
+        <v>181.1666666666667</v>
+      </c>
+      <c r="W4" t="n">
         <v>1</v>
       </c>
-      <c r="W4" t="n">
-        <v>71.46875</v>
-      </c>
       <c r="X4" t="n">
-        <v>3939843.75</v>
+        <v>71.89583333333333</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.40625</v>
+        <v>4365625</v>
       </c>
       <c r="Z4" t="n">
-        <v>25.82315592903828</v>
+        <v>76.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>179.4782913165266</v>
+        <v>25.80849673202614</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.2562558356676</v>
+        <v>179.374387254902</v>
       </c>
       <c r="AC4" t="n">
-        <v>74.53842203548086</v>
+        <v>1.238929738562091</v>
       </c>
       <c r="AD4" t="n">
-        <v>7604421.101774042</v>
+        <v>74.52258986928105</v>
       </c>
       <c r="AE4" t="n">
-        <v>77.49913632119514</v>
+        <v>7528868.464052287</v>
       </c>
       <c r="AF4" t="n">
-        <v>23.63474607234198</v>
+        <v>77.42939133986928</v>
       </c>
       <c r="AG4" t="n">
-        <v>180.9953076882927</v>
+        <v>23.58280305765835</v>
       </c>
       <c r="AH4" t="n">
+        <v>180.7989123846844</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1</v>
       </c>
-      <c r="AI4" t="n">
-        <v>70.7673225812064</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>4134698.633076419</v>
+        <v>70.7173856778918</v>
       </c>
       <c r="AK4" t="n">
-        <v>76.27805441016986</v>
-      </c>
-      <c r="AL4" t="inlineStr">
+        <v>4001409.992253534</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>76.2524661563922</v>
+      </c>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>UDgEKBbq</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>nDP2jHyH</t>
         </is>
@@ -1097,84 +1105,85 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>25.01587301587302</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>180.3829365079365</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>1.035714285714286</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>74.29960317460316</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>8950000</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>78.18650793650794</v>
       </c>
-      <c r="T5" t="n">
-        <v>25.92129629629629</v>
-      </c>
       <c r="U5" t="n">
-        <v>186.5416666666667</v>
+        <v>26.00396825396825</v>
       </c>
       <c r="V5" t="n">
-        <v>1.657407407407407</v>
+        <v>186.5535714285714</v>
       </c>
       <c r="W5" t="n">
-        <v>76.48611111111111</v>
+        <v>1.634920634920635</v>
       </c>
       <c r="X5" t="n">
-        <v>15328935.18518518</v>
+        <v>76.50595238095239</v>
       </c>
       <c r="Y5" t="n">
-        <v>79.9375</v>
+        <v>15173015.87301587</v>
       </c>
       <c r="Z5" t="n">
-        <v>26.77285236502627</v>
+        <v>79.91071428571429</v>
       </c>
       <c r="AA5" t="n">
-        <v>178.975347985348</v>
+        <v>26.84670036485254</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.104925147316452</v>
+        <v>179.0409294871795</v>
       </c>
       <c r="AC5" t="n">
-        <v>72.64460742156395</v>
+        <v>1.114536776629168</v>
       </c>
       <c r="AD5" t="n">
-        <v>4917440.476190476</v>
+        <v>72.66062240295935</v>
       </c>
       <c r="AE5" t="n">
-        <v>74.56647077560122</v>
+        <v>4948214.962121212</v>
       </c>
       <c r="AF5" t="n">
-        <v>24.38625265895832</v>
+        <v>74.47861647410561</v>
       </c>
       <c r="AG5" t="n">
-        <v>183.9209228428213</v>
+        <v>24.4046377432552</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5843737494998</v>
+        <v>184.2558074874687</v>
       </c>
       <c r="AI5" t="n">
-        <v>75.43027026600114</v>
+        <v>1.577993697478991</v>
       </c>
       <c r="AJ5" t="n">
-        <v>12577507.92422232</v>
+        <v>75.40981981608434</v>
       </c>
       <c r="AK5" t="n">
-        <v>80.75036356647922</v>
-      </c>
-      <c r="AL5" t="inlineStr">
+        <v>12487819.43369453</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>80.67323478733599</v>
+      </c>
+      <c r="AM5" t="inlineStr">
         <is>
           <t>WC1tKXIF</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
@@ -1242,66 +1251,67 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>26.13690476190476</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>181.5</v>
+        <v>26.10648148148148</v>
       </c>
       <c r="V6" t="n">
+        <v>182</v>
+      </c>
+      <c r="W6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" t="n">
-        <v>69.40873015873015</v>
-      </c>
       <c r="X6" t="n">
-        <v>1997470.238095238</v>
+        <v>69.41512345679013</v>
       </c>
       <c r="Y6" t="n">
-        <v>73.11706349206349</v>
+        <v>1989351.851851852</v>
       </c>
       <c r="Z6" t="n">
-        <v>26.35643166357452</v>
+        <v>73.00771604938272</v>
       </c>
       <c r="AA6" t="n">
-        <v>183.8209029066172</v>
+        <v>26.46187770562771</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.05741341991342</v>
+        <v>183.7932900432901</v>
       </c>
       <c r="AC6" t="n">
-        <v>72.52097247990106</v>
+        <v>1.050236742424242</v>
       </c>
       <c r="AD6" t="n">
-        <v>6964055.156153371</v>
+        <v>72.76418425324675</v>
       </c>
       <c r="AE6" t="n">
-        <v>75.95047928262214</v>
+        <v>7103756.594967533</v>
       </c>
       <c r="AF6" t="n">
-        <v>27.45431225121627</v>
+        <v>76.1150027056277</v>
       </c>
       <c r="AG6" t="n">
-        <v>181.4008452503808</v>
+        <v>27.14471199785957</v>
       </c>
       <c r="AH6" t="n">
+        <v>180.8994228490616</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1</v>
       </c>
-      <c r="AI6" t="n">
-        <v>69.11993709764607</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>1765501.867413632</v>
+        <v>69.03155601421855</v>
       </c>
       <c r="AK6" t="n">
-        <v>72.33573639982309</v>
-      </c>
-      <c r="AL6" t="inlineStr">
+        <v>1834032.316630356</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>72.47347398998585</v>
+      </c>
+      <c r="AM6" t="inlineStr">
         <is>
           <t>KWIuYKwG</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>Qkg2vOrk</t>
         </is>
@@ -1363,84 +1373,85 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>23.75</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>182.875</v>
+        <v>23.8125</v>
       </c>
       <c r="P7" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.125</v>
       </c>
-      <c r="Q7" t="n">
-        <v>75.125</v>
-      </c>
       <c r="R7" t="n">
-        <v>12662500</v>
+        <v>75.5</v>
       </c>
       <c r="S7" t="n">
-        <v>80.375</v>
+        <v>13200000</v>
       </c>
       <c r="T7" t="n">
-        <v>26.16666666666666</v>
+        <v>80.1875</v>
       </c>
       <c r="U7" t="n">
-        <v>181.4222222222222</v>
+        <v>25.82407407407408</v>
       </c>
       <c r="V7" t="n">
-        <v>2.805555555555556</v>
+        <v>181.6296296296296</v>
       </c>
       <c r="W7" t="n">
-        <v>81.90555555555555</v>
+        <v>2.726851851851852</v>
       </c>
       <c r="X7" t="n">
-        <v>46715833.33333333</v>
+        <v>81.18055555555556</v>
       </c>
       <c r="Y7" t="n">
-        <v>85.94444444444444</v>
+        <v>43268749.99999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.33493666697448</v>
+        <v>85.69444444444446</v>
       </c>
       <c r="AA7" t="n">
-        <v>180.1266652814972</v>
+        <v>24.13424367027308</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.119127651060424</v>
+        <v>179.8791812218283</v>
       </c>
       <c r="AC7" t="n">
-        <v>72.60331517222274</v>
+        <v>1.092654839713663</v>
       </c>
       <c r="AD7" t="n">
-        <v>6507113.345338136</v>
+        <v>72.77660444131033</v>
       </c>
       <c r="AE7" t="n">
-        <v>76.89876873826454</v>
+        <v>6628187.724584784</v>
       </c>
       <c r="AF7" t="n">
-        <v>23.84827369544309</v>
+        <v>77.33107698401815</v>
       </c>
       <c r="AG7" t="n">
-        <v>180.441840069361</v>
+        <v>23.63428493805816</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.337283509895186</v>
+        <v>180.2672918788727</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.6264388211425</v>
+        <v>2.31785034388556</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38270092.80905344</v>
+        <v>79.31517942304512</v>
       </c>
       <c r="AK7" t="n">
-        <v>85.24200645170349</v>
-      </c>
-      <c r="AL7" t="inlineStr">
+        <v>38762751.66246722</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>85.18902837251328</v>
+      </c>
+      <c r="AM7" t="inlineStr">
         <is>
           <t>UDgEKBbq</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
@@ -1502,84 +1513,85 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>25.81139971139971</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>181.7988455988456</v>
+        <v>25.76543209876543</v>
       </c>
       <c r="P8" t="n">
-        <v>1.703318903318903</v>
+        <v>181.5617283950617</v>
       </c>
       <c r="Q8" t="n">
-        <v>79.01890331890331</v>
+        <v>1.685409652076319</v>
       </c>
       <c r="R8" t="n">
-        <v>24489610.38961039</v>
+        <v>79.24904601571269</v>
       </c>
       <c r="S8" t="n">
-        <v>82.08124098124098</v>
+        <v>25156060.60606061</v>
       </c>
       <c r="T8" t="n">
-        <v>29.24682539682539</v>
+        <v>82.37530864197531</v>
       </c>
       <c r="U8" t="n">
-        <v>179.8547619047619</v>
+        <v>29.20208333333333</v>
       </c>
       <c r="V8" t="n">
-        <v>1.392857142857143</v>
+        <v>179.6923611111111</v>
       </c>
       <c r="W8" t="n">
-        <v>75.71904761904761</v>
+        <v>1.385416666666667</v>
       </c>
       <c r="X8" t="n">
-        <v>7734007.936507936</v>
+        <v>75.74027777777778</v>
       </c>
       <c r="Y8" t="n">
-        <v>76.87619047619049</v>
+        <v>7840868.055555556</v>
       </c>
       <c r="Z8" t="n">
-        <v>24.39047686268183</v>
+        <v>76.90555555555557</v>
       </c>
       <c r="AA8" t="n">
-        <v>180.9509531875992</v>
+        <v>24.31152571261267</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.600210938130193</v>
+        <v>181.0136123136123</v>
       </c>
       <c r="AC8" t="n">
-        <v>75.17326638165149</v>
+        <v>1.638903423468641</v>
       </c>
       <c r="AD8" t="n">
-        <v>15709285.8789761</v>
+        <v>75.01122926992493</v>
       </c>
       <c r="AE8" t="n">
-        <v>80.11120513027345</v>
+        <v>15743431.23000188</v>
       </c>
       <c r="AF8" t="n">
-        <v>28.82970790424207</v>
+        <v>80.05106614802267</v>
       </c>
       <c r="AG8" t="n">
-        <v>179.8954182463499</v>
+        <v>28.85099441621181</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.419048515321807</v>
+        <v>179.9959909655562</v>
       </c>
       <c r="AI8" t="n">
-        <v>74.12472103465893</v>
+        <v>1.429167450906581</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6178234.653545211</v>
+        <v>74.09038090532655</v>
       </c>
       <c r="AK8" t="n">
-        <v>75.34734209889488</v>
-      </c>
-      <c r="AL8" t="inlineStr">
+        <v>6061892.82185206</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75.34142433653304</v>
+      </c>
+      <c r="AM8" t="inlineStr">
         <is>
           <t>IJEltJ2H</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>EJmuzs93</t>
         </is>
@@ -1641,86 +1653,629 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>28.55787037037037</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>182.9606481481482</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>1.349537037037037</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>76.37037037037038</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>10193981.48148148</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>77.4375</v>
       </c>
-      <c r="T9" t="n">
-        <v>25.73333333333333</v>
-      </c>
       <c r="U9" t="n">
-        <v>182.4</v>
+        <v>25.825</v>
       </c>
       <c r="V9" t="n">
-        <v>3.366666666666667</v>
+        <v>182.255</v>
       </c>
       <c r="W9" t="n">
-        <v>85.93333333333332</v>
+        <v>3.04</v>
       </c>
       <c r="X9" t="n">
-        <v>79483333.33333333</v>
+        <v>85.35999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>88.86666666666667</v>
+        <v>72302500</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.46533098226462</v>
+        <v>88.185</v>
       </c>
       <c r="AA9" t="n">
-        <v>180.9545636158909</v>
+        <v>27.50838874378157</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.132863449797088</v>
+        <v>181.0505191759959</v>
       </c>
       <c r="AC9" t="n">
-        <v>74.77383742624018</v>
+        <v>1.138691774084604</v>
       </c>
       <c r="AD9" t="n">
-        <v>8073784.675786965</v>
+        <v>74.95540890727771</v>
       </c>
       <c r="AE9" t="n">
-        <v>76.72069171611506</v>
+        <v>8302337.576117135</v>
       </c>
       <c r="AF9" t="n">
-        <v>25.68593355020821</v>
+        <v>76.77770971859452</v>
       </c>
       <c r="AG9" t="n">
-        <v>181.0941356299605</v>
+        <v>25.70711498349527</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.869857963428287</v>
+        <v>180.6240206946476</v>
       </c>
       <c r="AI9" t="n">
-        <v>84.44514330698541</v>
+        <v>2.915225784420831</v>
       </c>
       <c r="AJ9" t="n">
-        <v>65112391.2284212</v>
+        <v>84.4372313440296</v>
       </c>
       <c r="AK9" t="n">
-        <v>87.83036277938974</v>
-      </c>
-      <c r="AL9" t="inlineStr">
+        <v>64874513.35309953</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>87.88012134303413</v>
+      </c>
+      <c r="AM9" t="inlineStr">
         <is>
           <t>4AuIPRuq</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45523.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>148</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>26.3125</v>
+      </c>
+      <c r="V10" t="n">
+        <v>182.1875</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="X10" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3062500</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>25.58255948844185</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>179.811958520782</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>69.70650199473728</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2496377.995642702</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>74.35244602891662</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>28.10554029304029</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>179.6579212454212</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.061675824175824</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>71.02142857142857</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2107696.886446886</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>72.99987789987789</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>IilCZTta</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45523.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>148</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>27.16319444444444</v>
+      </c>
+      <c r="P11" t="n">
+        <v>186.6701388888889</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.701388888888889</v>
+      </c>
+      <c r="R11" t="n">
+        <v>76.86458333333333</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11181944.44444444</v>
+      </c>
+      <c r="T11" t="n">
+        <v>79.69097222222223</v>
+      </c>
+      <c r="U11" t="n">
+        <v>27.98024691358025</v>
+      </c>
+      <c r="V11" t="n">
+        <v>180.0685185185185</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.381172839506173</v>
+      </c>
+      <c r="X11" t="n">
+        <v>82.3641975308642</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>35168209.87654321</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>84.08086419753084</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>28.60393957893958</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>183.9318302068302</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.758246845746846</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>76.97246642246643</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9382820.929070929</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>79.04716533466532</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>26.22707631874299</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>180.4407126823793</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.797292368125701</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>78.85725308641976</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>21976714.36588103</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>82.13925364758698</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>148</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1484</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>26.37732884399551</v>
+      </c>
+      <c r="P12" t="n">
+        <v>182.8641975308642</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.597867564534231</v>
+      </c>
+      <c r="R12" t="n">
+        <v>79.41111111111111</v>
+      </c>
+      <c r="S12" t="n">
+        <v>23003254.76992144</v>
+      </c>
+      <c r="T12" t="n">
+        <v>82.17519640852974</v>
+      </c>
+      <c r="U12" t="n">
+        <v>25.82407407407408</v>
+      </c>
+      <c r="V12" t="n">
+        <v>181.6296296296296</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.726851851851852</v>
+      </c>
+      <c r="X12" t="n">
+        <v>81.18055555555556</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>43268749.99999999</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>85.69444444444446</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>27.13197486469797</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>181.8494231956703</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.509932348988413</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>76.35683611201918</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>13462277.18753405</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>79.53628246340489</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>23.63428493805816</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>180.2672918788727</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.31785034388556</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>79.31517942304512</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38762751.66246722</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>85.18902837251328</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1484</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>25.825</v>
+      </c>
+      <c r="P13" t="n">
+        <v>182.255</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R13" t="n">
+        <v>85.35999999999999</v>
+      </c>
+      <c r="S13" t="n">
+        <v>72302500</v>
+      </c>
+      <c r="T13" t="n">
+        <v>88.185</v>
+      </c>
+      <c r="U13" t="n">
+        <v>28.55787037037037</v>
+      </c>
+      <c r="V13" t="n">
+        <v>182.9606481481482</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.349537037037037</v>
+      </c>
+      <c r="X13" t="n">
+        <v>76.37037037037038</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10193981.48148148</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>77.4375</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>25.70711498349527</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>180.6240206946476</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.915225784420831</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>84.4372313440296</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>64874513.35309953</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>87.88012134303413</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>27.50838874378157</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>181.0505191759959</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.138691774084604</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>74.95540890727771</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>8302337.576117135</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>76.77770971859452</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/spain/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_filled.xlsx
@@ -687,22 +687,22 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>26.37732884399551</v>
+        <v>26.36893939393939</v>
       </c>
       <c r="P2" t="n">
-        <v>182.8641975308642</v>
+        <v>182.7083333333334</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.597867564534231</v>
+        <v>1.630934343434344</v>
       </c>
       <c r="R2" t="n">
-        <v>79.41111111111111</v>
+        <v>79.50416666666666</v>
       </c>
       <c r="S2" t="n">
-        <v>23003254.76992144</v>
+        <v>23455050.50505051</v>
       </c>
       <c r="T2" t="n">
-        <v>82.17519640852974</v>
+        <v>82.25265151515151</v>
       </c>
       <c r="U2" t="n">
         <v>26.66071428571428</v>
@@ -723,22 +723,22 @@
         <v>79.125</v>
       </c>
       <c r="AA2" t="n">
-        <v>27.13197486469797</v>
+        <v>27.01436360627817</v>
       </c>
       <c r="AB2" t="n">
-        <v>181.8494231956703</v>
+        <v>182.0443326512739</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.509932348988413</v>
+        <v>1.497808430092946</v>
       </c>
       <c r="AD2" t="n">
-        <v>76.35683611201918</v>
+        <v>76.06315123557687</v>
       </c>
       <c r="AE2" t="n">
-        <v>13462277.18753405</v>
+        <v>12926339.73218069</v>
       </c>
       <c r="AF2" t="n">
-        <v>79.53628246340489</v>
+        <v>79.39481120272501</v>
       </c>
       <c r="AG2" t="n">
         <v>24.82088293650794</v>
@@ -985,22 +985,22 @@
         <v>78.24305555555556</v>
       </c>
       <c r="U4" t="n">
-        <v>24.14583333333333</v>
+        <v>24.05</v>
       </c>
       <c r="V4" t="n">
-        <v>181.1666666666667</v>
+        <v>181</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>71.89583333333333</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>4365625</v>
+        <v>4163750</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.75</v>
+        <v>76.575</v>
       </c>
       <c r="AA4" t="n">
         <v>25.80849673202614</v>
@@ -1021,22 +1021,22 @@
         <v>77.42939133986928</v>
       </c>
       <c r="AG4" t="n">
-        <v>23.58280305765835</v>
+        <v>23.6080343922466</v>
       </c>
       <c r="AH4" t="n">
-        <v>180.7989123846844</v>
+        <v>180.8511573851509</v>
       </c>
       <c r="AI4" t="n">
         <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70.7173856778918</v>
+        <v>70.78324936381875</v>
       </c>
       <c r="AK4" t="n">
-        <v>4001409.992253534</v>
+        <v>4078223.14604713</v>
       </c>
       <c r="AL4" t="n">
-        <v>76.2524661563922</v>
+        <v>76.295929187846</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
@@ -1515,22 +1515,22 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>25.76543209876543</v>
+        <v>25.82361111111111</v>
       </c>
       <c r="P8" t="n">
-        <v>181.5617283950617</v>
+        <v>181.7444444444444</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.685409652076319</v>
+        <v>1.683585858585858</v>
       </c>
       <c r="R8" t="n">
-        <v>79.24904601571269</v>
+        <v>79.13017676767677</v>
       </c>
       <c r="S8" t="n">
-        <v>25156060.60606061</v>
+        <v>24644318.18181818</v>
       </c>
       <c r="T8" t="n">
-        <v>82.37530864197531</v>
+        <v>82.18472222222221</v>
       </c>
       <c r="U8" t="n">
         <v>29.20208333333333</v>
@@ -1551,22 +1551,22 @@
         <v>76.90555555555557</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.31152571261267</v>
+        <v>24.31785773103708</v>
       </c>
       <c r="AB8" t="n">
-        <v>181.0136123136123</v>
+        <v>180.9392268962921</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.638903423468641</v>
+        <v>1.626375047054395</v>
       </c>
       <c r="AD8" t="n">
-        <v>75.01122926992493</v>
+        <v>75.11589379823076</v>
       </c>
       <c r="AE8" t="n">
-        <v>15743431.23000188</v>
+        <v>15954702.52505646</v>
       </c>
       <c r="AF8" t="n">
-        <v>80.05106614802267</v>
+        <v>80.13897115565594</v>
       </c>
       <c r="AG8" t="n">
         <v>28.85099441621181</v>
@@ -1673,22 +1673,22 @@
         <v>77.4375</v>
       </c>
       <c r="U9" t="n">
-        <v>25.825</v>
+        <v>25.83125</v>
       </c>
       <c r="V9" t="n">
-        <v>182.255</v>
+        <v>182.39375</v>
       </c>
       <c r="W9" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="X9" t="n">
-        <v>85.35999999999999</v>
+        <v>85.57499999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>72302500</v>
+        <v>74753125</v>
       </c>
       <c r="Z9" t="n">
-        <v>88.185</v>
+        <v>88.43125000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>27.50838874378157</v>
@@ -1709,22 +1709,22 @@
         <v>76.77770971859452</v>
       </c>
       <c r="AG9" t="n">
-        <v>25.70711498349527</v>
+        <v>25.60019185643218</v>
       </c>
       <c r="AH9" t="n">
-        <v>180.6240206946476</v>
+        <v>180.8192107814786</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.915225784420831</v>
+        <v>2.912441507473435</v>
       </c>
       <c r="AJ9" t="n">
-        <v>84.4372313440296</v>
+        <v>84.46844776203329</v>
       </c>
       <c r="AK9" t="n">
-        <v>64874513.35309953</v>
+        <v>66042421.27223697</v>
       </c>
       <c r="AL9" t="n">
-        <v>87.88012134303413</v>
+        <v>87.9041990109134</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
@@ -1931,76 +1931,76 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>27.16319444444444</v>
+        <v>26.67592592592592</v>
       </c>
       <c r="P11" t="n">
-        <v>186.6701388888889</v>
+        <v>186.2268518518518</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.701388888888889</v>
+        <v>1.643518518518519</v>
       </c>
       <c r="R11" t="n">
-        <v>76.86458333333333</v>
+        <v>76.4861111111111</v>
       </c>
       <c r="S11" t="n">
-        <v>11181944.44444444</v>
+        <v>10759259.25925926</v>
       </c>
       <c r="T11" t="n">
-        <v>79.69097222222223</v>
+        <v>79.33796296296296</v>
       </c>
       <c r="U11" t="n">
-        <v>27.98024691358025</v>
+        <v>28.02777777777778</v>
       </c>
       <c r="V11" t="n">
-        <v>180.0685185185185</v>
+        <v>180.0520833333333</v>
       </c>
       <c r="W11" t="n">
-        <v>2.381172839506173</v>
+        <v>2.366319444444445</v>
       </c>
       <c r="X11" t="n">
-        <v>82.3641975308642</v>
+        <v>82.40972222222223</v>
       </c>
       <c r="Y11" t="n">
-        <v>35168209.87654321</v>
+        <v>35282986.11111111</v>
       </c>
       <c r="Z11" t="n">
-        <v>84.08086419753084</v>
+        <v>84.06597222222221</v>
       </c>
       <c r="AA11" t="n">
-        <v>28.60393957893958</v>
+        <v>28.78880702630703</v>
       </c>
       <c r="AB11" t="n">
-        <v>183.9318302068302</v>
+        <v>184.032683982684</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.758246845746846</v>
+        <v>1.782715201465201</v>
       </c>
       <c r="AD11" t="n">
-        <v>76.97246642246643</v>
+        <v>77.12527472527472</v>
       </c>
       <c r="AE11" t="n">
-        <v>9382820.929070929</v>
+        <v>9450986.045204796</v>
       </c>
       <c r="AF11" t="n">
-        <v>79.04716533466532</v>
+        <v>79.23274850149849</v>
       </c>
       <c r="AG11" t="n">
-        <v>26.22707631874299</v>
+        <v>26.05407196969697</v>
       </c>
       <c r="AH11" t="n">
-        <v>180.4407126823793</v>
+        <v>180.3499684343434</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.797292368125701</v>
+        <v>1.744176136363636</v>
       </c>
       <c r="AJ11" t="n">
-        <v>78.85725308641976</v>
+        <v>78.8046875</v>
       </c>
       <c r="AK11" t="n">
-        <v>21976714.36588103</v>
+        <v>22024498.10606061</v>
       </c>
       <c r="AL11" t="n">
-        <v>82.13925364758698</v>
+        <v>82.19138257575757</v>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
@@ -2064,22 +2064,22 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>26.37732884399551</v>
+        <v>26.36893939393939</v>
       </c>
       <c r="P12" t="n">
-        <v>182.8641975308642</v>
+        <v>182.7083333333334</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.597867564534231</v>
+        <v>1.630934343434344</v>
       </c>
       <c r="R12" t="n">
-        <v>79.41111111111111</v>
+        <v>79.50416666666666</v>
       </c>
       <c r="S12" t="n">
-        <v>23003254.76992144</v>
+        <v>23455050.50505051</v>
       </c>
       <c r="T12" t="n">
-        <v>82.17519640852974</v>
+        <v>82.25265151515151</v>
       </c>
       <c r="U12" t="n">
         <v>25.82407407407408</v>
@@ -2100,22 +2100,22 @@
         <v>85.69444444444446</v>
       </c>
       <c r="AA12" t="n">
-        <v>27.13197486469797</v>
+        <v>27.01436360627817</v>
       </c>
       <c r="AB12" t="n">
-        <v>181.8494231956703</v>
+        <v>182.0443326512739</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.509932348988413</v>
+        <v>1.497808430092946</v>
       </c>
       <c r="AD12" t="n">
-        <v>76.35683611201918</v>
+        <v>76.06315123557687</v>
       </c>
       <c r="AE12" t="n">
-        <v>13462277.18753405</v>
+        <v>12926339.73218069</v>
       </c>
       <c r="AF12" t="n">
-        <v>79.53628246340489</v>
+        <v>79.39481120272501</v>
       </c>
       <c r="AG12" t="n">
         <v>23.63428493805816</v>
@@ -2197,22 +2197,22 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>25.825</v>
+        <v>25.83125</v>
       </c>
       <c r="P13" t="n">
-        <v>182.255</v>
+        <v>182.39375</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="R13" t="n">
-        <v>85.35999999999999</v>
+        <v>85.57499999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>72302500</v>
+        <v>74753125</v>
       </c>
       <c r="T13" t="n">
-        <v>88.185</v>
+        <v>88.43125000000001</v>
       </c>
       <c r="U13" t="n">
         <v>28.55787037037037</v>
@@ -2233,22 +2233,22 @@
         <v>77.4375</v>
       </c>
       <c r="AA13" t="n">
-        <v>25.70711498349527</v>
+        <v>25.60019185643218</v>
       </c>
       <c r="AB13" t="n">
-        <v>180.6240206946476</v>
+        <v>180.8192107814786</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.915225784420831</v>
+        <v>2.912441507473435</v>
       </c>
       <c r="AD13" t="n">
-        <v>84.4372313440296</v>
+        <v>84.46844776203329</v>
       </c>
       <c r="AE13" t="n">
-        <v>64874513.35309953</v>
+        <v>66042421.27223697</v>
       </c>
       <c r="AF13" t="n">
-        <v>87.88012134303413</v>
+        <v>87.9041990109134</v>
       </c>
       <c r="AG13" t="n">
         <v>27.50838874378157</v>

--- a/p6_deployment/data/spain/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AO13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,130 +500,135 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>id_team_away_rival_team</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -686,84 +691,89 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>26.36893939393939</v>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
       </c>
       <c r="P2" t="n">
-        <v>182.7083333333334</v>
+        <v>25.29382716049383</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.630934343434344</v>
+        <v>182.8719135802469</v>
       </c>
       <c r="R2" t="n">
-        <v>79.50416666666666</v>
+        <v>1.514814814814815</v>
       </c>
       <c r="S2" t="n">
-        <v>23455050.50505051</v>
+        <v>78.88672839506172</v>
       </c>
       <c r="T2" t="n">
-        <v>82.25265151515151</v>
+        <v>23387500</v>
       </c>
       <c r="U2" t="n">
-        <v>26.66071428571428</v>
+        <v>82.15833333333333</v>
       </c>
       <c r="V2" t="n">
-        <v>183.6785714285714</v>
+        <v>26.28993055555555</v>
       </c>
       <c r="W2" t="n">
-        <v>1.339285714285714</v>
+        <v>183.5694444444444</v>
       </c>
       <c r="X2" t="n">
-        <v>76.46428571428571</v>
+        <v>1.321180555555555</v>
       </c>
       <c r="Y2" t="n">
-        <v>12815178.57142857</v>
+        <v>76.14409722222223</v>
       </c>
       <c r="Z2" t="n">
-        <v>79.125</v>
+        <v>12212456.59722222</v>
       </c>
       <c r="AA2" t="n">
-        <v>27.01436360627817</v>
+        <v>79.30381944444444</v>
       </c>
       <c r="AB2" t="n">
-        <v>182.0443326512739</v>
+        <v>25.26073692103104</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.497808430092946</v>
+        <v>181.7650546077017</v>
       </c>
       <c r="AD2" t="n">
-        <v>76.06315123557687</v>
+        <v>1.354055258467023</v>
       </c>
       <c r="AE2" t="n">
-        <v>12926339.73218069</v>
+        <v>75.40366975072858</v>
       </c>
       <c r="AF2" t="n">
-        <v>79.39481120272501</v>
+        <v>13228080.94955154</v>
       </c>
       <c r="AG2" t="n">
-        <v>24.82088293650794</v>
+        <v>79.78000311235606</v>
       </c>
       <c r="AH2" t="n">
-        <v>184.5580853174603</v>
+        <v>24.57832341269841</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.131795634920635</v>
+        <v>184.7292162698413</v>
       </c>
       <c r="AJ2" t="n">
-        <v>70.98271329365079</v>
+        <v>1.121081349206349</v>
       </c>
       <c r="AK2" t="n">
-        <v>5247843.625992063</v>
+        <v>71.78727678571428</v>
       </c>
       <c r="AL2" t="n">
-        <v>76.04432043650795</v>
-      </c>
-      <c r="AM2" t="inlineStr">
+        <v>5391410.590277778</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>77.2749255952381</v>
+      </c>
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0Q3vjDhH</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>p2dFnNso</t>
         </is>
@@ -825,85 +835,94 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>27.60416666666667</v>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
       </c>
       <c r="P3" t="n">
-        <v>182.1875</v>
+        <v>27.79365079365079</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.854166666666667</v>
+        <v>182.0119047619048</v>
       </c>
       <c r="R3" t="n">
-        <v>76.33333333333333</v>
+        <v>1.871031746031746</v>
       </c>
       <c r="S3" t="n">
-        <v>11460416.66666667</v>
+        <v>76.39682539682541</v>
       </c>
       <c r="T3" t="n">
-        <v>78.95833333333333</v>
+        <v>11400793.65079365</v>
       </c>
       <c r="U3" t="n">
-        <v>25.24583333333333</v>
+        <v>78.75396825396827</v>
       </c>
       <c r="V3" t="n">
-        <v>181.1972222222222</v>
+        <v>24.975</v>
       </c>
       <c r="W3" t="n">
-        <v>1.456944444444445</v>
+        <v>182.3375</v>
       </c>
       <c r="X3" t="n">
-        <v>79.66666666666667</v>
+        <v>1.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>26460555.55555556</v>
+        <v>78.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>82.91249999999999</v>
+        <v>25057500</v>
       </c>
       <c r="AA3" t="n">
-        <v>28.11496175393234</v>
+        <v>82.72499999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>183.2451330532213</v>
+        <v>28.12487599206349</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.024999999999999</v>
+        <v>183.1067708333333</v>
       </c>
       <c r="AD3" t="n">
-        <v>76.09579293255764</v>
+        <v>2.020833333333333</v>
       </c>
       <c r="AE3" t="n">
-        <v>10877746.98340875</v>
+        <v>76.16133432539682</v>
       </c>
       <c r="AF3" t="n">
-        <v>79.10886931695754</v>
+        <v>11012524.8015873</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.46636663774822</v>
+        <v>79.10391865079364</v>
       </c>
       <c r="AH3" t="n">
-        <v>178.3515415140415</v>
+        <v>23.97150178435219</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.138280798149219</v>
+        <v>178.3522263539283</v>
       </c>
       <c r="AJ3" t="n">
-        <v>74.84877096587624</v>
+        <v>1.119713175602049</v>
       </c>
       <c r="AK3" t="n">
-        <v>15307687.00597648</v>
+        <v>75.24845503704914</v>
       </c>
       <c r="AL3" t="n">
-        <v>80.46891467450678</v>
-      </c>
-      <c r="AM3" t="inlineStr">
+        <v>15947498.63789909</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>80.95702367331373</v>
+      </c>
+      <c r="AN3" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>A7v4ruhp</t>
         </is>
@@ -965,85 +984,90 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>27.24305555555555</v>
-      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>182.0532407407408</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.451388888888889</v>
+        <v>182.2539682539683</v>
       </c>
       <c r="R4" t="n">
-        <v>75.18287037037037</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="S4" t="n">
-        <v>8295833.333333333</v>
+        <v>75.03968253968254</v>
       </c>
       <c r="T4" t="n">
-        <v>78.24305555555556</v>
+        <v>8103174.603174603</v>
       </c>
       <c r="U4" t="n">
-        <v>24.05</v>
+        <v>78.16507936507936</v>
       </c>
       <c r="V4" t="n">
-        <v>181</v>
+        <v>23.64814814814815</v>
       </c>
       <c r="W4" t="n">
+        <v>182.0972222222223</v>
+      </c>
+      <c r="X4" t="n">
         <v>1</v>
       </c>
-      <c r="X4" t="n">
-        <v>71.59999999999999</v>
-      </c>
       <c r="Y4" t="n">
-        <v>4163750</v>
+        <v>71.25462962962963</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.575</v>
+        <v>4062500</v>
       </c>
       <c r="AA4" t="n">
-        <v>25.80849673202614</v>
+        <v>77.19907407407408</v>
       </c>
       <c r="AB4" t="n">
-        <v>179.374387254902</v>
+        <v>25.30606060606061</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.238929738562091</v>
+        <v>180.0204816017316</v>
       </c>
       <c r="AD4" t="n">
-        <v>74.52258986928105</v>
+        <v>1.191044372294372</v>
       </c>
       <c r="AE4" t="n">
-        <v>7528868.464052287</v>
+        <v>73.72873376623377</v>
       </c>
       <c r="AF4" t="n">
-        <v>77.42939133986928</v>
+        <v>6829829.545454545</v>
       </c>
       <c r="AG4" t="n">
-        <v>23.6080343922466</v>
+        <v>77.36168831168831</v>
       </c>
       <c r="AH4" t="n">
-        <v>180.8511573851509</v>
+        <v>23.54257246376812</v>
       </c>
       <c r="AI4" t="n">
+        <v>180.9154589371981</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>70.78324936381875</v>
-      </c>
       <c r="AK4" t="n">
-        <v>4078223.14604713</v>
+        <v>70.68184955141476</v>
       </c>
       <c r="AL4" t="n">
-        <v>76.295929187846</v>
-      </c>
-      <c r="AM4" t="inlineStr">
+        <v>3850310.559006211</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>76.42809696342304</v>
+      </c>
+      <c r="AN4" t="inlineStr">
         <is>
           <t>UDgEKBbq</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>nDP2jHyH</t>
         </is>
@@ -1105,85 +1129,94 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>25.01587301587302</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
       </c>
       <c r="P5" t="n">
-        <v>180.3829365079365</v>
+        <v>24.88293650793651</v>
       </c>
       <c r="Q5" t="n">
+        <v>179.6071428571429</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.035714285714286</v>
       </c>
-      <c r="R5" t="n">
-        <v>74.29960317460316</v>
-      </c>
       <c r="S5" t="n">
-        <v>8950000</v>
+        <v>74.91269841269842</v>
       </c>
       <c r="T5" t="n">
-        <v>78.18650793650794</v>
+        <v>10446230.15873016</v>
       </c>
       <c r="U5" t="n">
-        <v>26.00396825396825</v>
+        <v>78.62103174603173</v>
       </c>
       <c r="V5" t="n">
-        <v>186.5535714285714</v>
+        <v>28.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.634920634920635</v>
+        <v>184.9385416666667</v>
       </c>
       <c r="X5" t="n">
-        <v>76.50595238095239</v>
+        <v>2.04375</v>
       </c>
       <c r="Y5" t="n">
-        <v>15173015.87301587</v>
+        <v>77.81041666666667</v>
       </c>
       <c r="Z5" t="n">
-        <v>79.91071428571429</v>
+        <v>13975069.44444444</v>
       </c>
       <c r="AA5" t="n">
-        <v>26.84670036485254</v>
+        <v>80.16354166666667</v>
       </c>
       <c r="AB5" t="n">
-        <v>179.0409294871795</v>
+        <v>26.44866684920276</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.114536776629168</v>
+        <v>178.9288127608023</v>
       </c>
       <c r="AD5" t="n">
-        <v>72.66062240295935</v>
+        <v>1.127813987567151</v>
       </c>
       <c r="AE5" t="n">
-        <v>4948214.962121212</v>
+        <v>73.06314045693168</v>
       </c>
       <c r="AF5" t="n">
-        <v>74.47861647410561</v>
+        <v>5660047.953964194</v>
       </c>
       <c r="AG5" t="n">
-        <v>24.4046377432552</v>
+        <v>75.2452737429484</v>
       </c>
       <c r="AH5" t="n">
-        <v>184.2558074874687</v>
+        <v>25.41943703301305</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.577993697478991</v>
+        <v>183.3490060669577</v>
       </c>
       <c r="AJ5" t="n">
-        <v>75.40981981608434</v>
+        <v>1.627527551829275</v>
       </c>
       <c r="AK5" t="n">
-        <v>12487819.43369453</v>
+        <v>75.61303539913295</v>
       </c>
       <c r="AL5" t="n">
-        <v>80.67323478733599</v>
-      </c>
-      <c r="AM5" t="inlineStr">
+        <v>11723820.80654535</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>80.07666880062476</v>
+      </c>
+      <c r="AN5" t="inlineStr">
         <is>
           <t>WC1tKXIF</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
@@ -1246,72 +1279,77 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11100000</v>
+      </c>
       <c r="U6" t="n">
-        <v>26.10648148148148</v>
-      </c>
-      <c r="V6" t="n">
-        <v>182</v>
-      </c>
-      <c r="W6" t="n">
+        <v>78</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>25.9863710941836</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>181.3564177142302</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.047224476911977</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>72.84928144771894</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>7850698.108315296</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>76.74345290126541</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>26.58624806565983</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>181.8278145873734</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1</v>
       </c>
-      <c r="X6" t="n">
-        <v>69.41512345679013</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1989351.851851852</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>73.00771604938272</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>26.46187770562771</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>183.7932900432901</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.050236742424242</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>72.76418425324675</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>7103756.594967533</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>76.1150027056277</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>27.14471199785957</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>180.8994228490616</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>69.03155601421855</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1834032.316630356</v>
+        <v>68.26875844743492</v>
       </c>
       <c r="AL6" t="n">
-        <v>72.47347398998585</v>
-      </c>
-      <c r="AM6" t="inlineStr">
+        <v>1745110.349209614</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>72.52199148890325</v>
+      </c>
+      <c r="AN6" t="inlineStr">
         <is>
           <t>KWIuYKwG</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>Qkg2vOrk</t>
         </is>
@@ -1373,85 +1411,94 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>23.8125</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
       </c>
       <c r="P7" t="n">
-        <v>182.625</v>
+        <v>22.61631944444444</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.125</v>
+        <v>181.2152777777778</v>
       </c>
       <c r="R7" t="n">
-        <v>75.5</v>
+        <v>1.107638888888889</v>
       </c>
       <c r="S7" t="n">
-        <v>13200000</v>
+        <v>71.19791666666666</v>
       </c>
       <c r="T7" t="n">
-        <v>80.1875</v>
+        <v>9185972.222222222</v>
       </c>
       <c r="U7" t="n">
-        <v>25.82407407407408</v>
+        <v>77.24131944444444</v>
       </c>
       <c r="V7" t="n">
-        <v>181.6296296296296</v>
+        <v>25.82291666666667</v>
       </c>
       <c r="W7" t="n">
-        <v>2.726851851851852</v>
+        <v>181.9045138888889</v>
       </c>
       <c r="X7" t="n">
-        <v>81.18055555555556</v>
+        <v>2.703125</v>
       </c>
       <c r="Y7" t="n">
-        <v>43268749.99999999</v>
+        <v>81.27951388888889</v>
       </c>
       <c r="Z7" t="n">
-        <v>85.69444444444446</v>
+        <v>44854861.1111111</v>
       </c>
       <c r="AA7" t="n">
-        <v>24.13424367027308</v>
+        <v>85.62326388888889</v>
       </c>
       <c r="AB7" t="n">
-        <v>179.8791812218283</v>
+        <v>23.93213716108453</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.092654839713663</v>
+        <v>180.335225943647</v>
       </c>
       <c r="AD7" t="n">
-        <v>72.77660444131033</v>
+        <v>1.078989898989899</v>
       </c>
       <c r="AE7" t="n">
-        <v>6628187.724584784</v>
+        <v>71.26668793195108</v>
       </c>
       <c r="AF7" t="n">
-        <v>77.33107698401815</v>
+        <v>5512095.95959596</v>
       </c>
       <c r="AG7" t="n">
-        <v>23.63428493805816</v>
+        <v>76.5253110047847</v>
       </c>
       <c r="AH7" t="n">
-        <v>180.2672918788727</v>
+        <v>23.60959682638745</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.31785034388556</v>
+        <v>180.5017145857893</v>
       </c>
       <c r="AJ7" t="n">
-        <v>79.31517942304512</v>
+        <v>2.318392015116844</v>
       </c>
       <c r="AK7" t="n">
-        <v>38762751.66246722</v>
+        <v>79.44544067679081</v>
       </c>
       <c r="AL7" t="n">
-        <v>85.18902837251328</v>
-      </c>
-      <c r="AM7" t="inlineStr">
+        <v>40567152.92224303</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>85.261088863463</v>
+      </c>
+      <c r="AN7" t="inlineStr">
         <is>
           <t>UDgEKBbq</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
@@ -1514,84 +1561,89 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>25.82361111111111</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>181.7444444444444</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>1.683585858585858</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>79.13017676767677</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>24644318.18181818</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>82.18472222222221</v>
       </c>
-      <c r="U8" t="n">
-        <v>29.20208333333333</v>
-      </c>
       <c r="V8" t="n">
-        <v>179.6923611111111</v>
+        <v>28.96006944444444</v>
       </c>
       <c r="W8" t="n">
-        <v>1.385416666666667</v>
+        <v>179.8767361111111</v>
       </c>
       <c r="X8" t="n">
-        <v>75.74027777777778</v>
+        <v>1.307291666666667</v>
       </c>
       <c r="Y8" t="n">
-        <v>7840868.055555556</v>
+        <v>75.40104166666667</v>
       </c>
       <c r="Z8" t="n">
-        <v>76.90555555555557</v>
+        <v>6664756.944444444</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.31785773103708</v>
+        <v>76.58159722222223</v>
       </c>
       <c r="AB8" t="n">
-        <v>180.9392268962921</v>
+        <v>24.47144915772633</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.626375047054395</v>
+        <v>180.5634263833992</v>
       </c>
       <c r="AD8" t="n">
-        <v>75.11589379823076</v>
+        <v>1.655547713156409</v>
       </c>
       <c r="AE8" t="n">
-        <v>15954702.52505646</v>
+        <v>75.58595485130812</v>
       </c>
       <c r="AF8" t="n">
-        <v>80.13897115565594</v>
+        <v>16626390.73675419</v>
       </c>
       <c r="AG8" t="n">
-        <v>28.85099441621181</v>
+        <v>80.28526079898363</v>
       </c>
       <c r="AH8" t="n">
-        <v>179.9959909655562</v>
+        <v>28.98191833751044</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.429167450906581</v>
+        <v>180.2723292606516</v>
       </c>
       <c r="AJ8" t="n">
-        <v>74.09038090532655</v>
+        <v>1.387305503341687</v>
       </c>
       <c r="AK8" t="n">
-        <v>6061892.82185206</v>
+        <v>74.64022034252297</v>
       </c>
       <c r="AL8" t="n">
-        <v>75.34142433653304</v>
-      </c>
-      <c r="AM8" t="inlineStr">
+        <v>5440179.485171262</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>75.37856881787803</v>
+      </c>
+      <c r="AN8" t="inlineStr">
         <is>
           <t>IJEltJ2H</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>EJmuzs93</t>
         </is>
@@ -1653,85 +1705,94 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>28.55787037037037</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
       </c>
       <c r="P9" t="n">
-        <v>182.9606481481482</v>
+        <v>27.7020202020202</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.349537037037037</v>
+        <v>183.1858585858586</v>
       </c>
       <c r="R9" t="n">
-        <v>76.37037037037038</v>
+        <v>1.286868686868687</v>
       </c>
       <c r="S9" t="n">
-        <v>10193981.48148148</v>
+        <v>75.77474747474747</v>
       </c>
       <c r="T9" t="n">
-        <v>77.4375</v>
+        <v>9570101.010101011</v>
       </c>
       <c r="U9" t="n">
-        <v>25.83125</v>
+        <v>77.64444444444445</v>
       </c>
       <c r="V9" t="n">
-        <v>182.39375</v>
+        <v>25.46157407407408</v>
       </c>
       <c r="W9" t="n">
-        <v>3.15</v>
+        <v>181.8776515151515</v>
       </c>
       <c r="X9" t="n">
-        <v>85.57499999999999</v>
+        <v>2.829040404040404</v>
       </c>
       <c r="Y9" t="n">
-        <v>74753125</v>
+        <v>83.26292087542087</v>
       </c>
       <c r="Z9" t="n">
-        <v>88.43125000000001</v>
+        <v>62781355.21885522</v>
       </c>
       <c r="AA9" t="n">
-        <v>27.50838874378157</v>
+        <v>87.10732323232325</v>
       </c>
       <c r="AB9" t="n">
-        <v>181.0505191759959</v>
+        <v>27.23065823065823</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.138691774084604</v>
+        <v>181.042402042402</v>
       </c>
       <c r="AD9" t="n">
-        <v>74.95540890727771</v>
+        <v>1.114080364080364</v>
       </c>
       <c r="AE9" t="n">
-        <v>8302337.576117135</v>
+        <v>74.57303807303806</v>
       </c>
       <c r="AF9" t="n">
-        <v>76.77770971859452</v>
+        <v>7789054.834054834</v>
       </c>
       <c r="AG9" t="n">
-        <v>25.60019185643218</v>
+        <v>76.64912864912864</v>
       </c>
       <c r="AH9" t="n">
-        <v>180.8192107814786</v>
+        <v>25.10080790919606</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.912441507473435</v>
+        <v>180.1463379000385</v>
       </c>
       <c r="AJ9" t="n">
-        <v>84.46844776203329</v>
+        <v>2.853098792654714</v>
       </c>
       <c r="AK9" t="n">
-        <v>66042421.27223697</v>
+        <v>83.29487480721033</v>
       </c>
       <c r="AL9" t="n">
-        <v>87.9041990109134</v>
-      </c>
-      <c r="AM9" t="inlineStr">
+        <v>65050253.78952187</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>87.42271092394448</v>
+      </c>
+      <c r="AN9" t="inlineStr">
         <is>
           <t>4AuIPRuq</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>U3wM1J72</t>
         </is>
@@ -1798,72 +1859,89 @@
           <t>69w4Rb2d</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>25.52777777777778</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>179.7673611111111</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="S10" t="n">
+        <v>70.22222222222221</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2883333.333333333</v>
+      </c>
       <c r="U10" t="n">
-        <v>26.3125</v>
+        <v>75.55555555555556</v>
       </c>
       <c r="V10" t="n">
-        <v>182.1875</v>
+        <v>27.06944444444444</v>
       </c>
       <c r="W10" t="n">
-        <v>1.125</v>
+        <v>182.5462962962963</v>
       </c>
       <c r="X10" t="n">
-        <v>70.75</v>
+        <v>1.162037037037037</v>
       </c>
       <c r="Y10" t="n">
-        <v>3062500</v>
+        <v>71.84722222222223</v>
       </c>
       <c r="Z10" t="n">
-        <v>75.125</v>
+        <v>3919444.444444444</v>
       </c>
       <c r="AA10" t="n">
-        <v>25.58255948844185</v>
+        <v>75.1388888888889</v>
       </c>
       <c r="AB10" t="n">
-        <v>179.811958520782</v>
+        <v>25.78370976336663</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>180.1519886068905</v>
       </c>
       <c r="AD10" t="n">
-        <v>69.70650199473728</v>
+        <v>1.174720123739732</v>
       </c>
       <c r="AE10" t="n">
-        <v>2496377.995642702</v>
+        <v>69.73968855218855</v>
       </c>
       <c r="AF10" t="n">
-        <v>74.35244602891662</v>
+        <v>2330018.579822501</v>
       </c>
       <c r="AG10" t="n">
-        <v>28.10554029304029</v>
+        <v>74.46470140244649</v>
       </c>
       <c r="AH10" t="n">
-        <v>179.6579212454212</v>
+        <v>27.06654325438262</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.061675824175824</v>
+        <v>179.4667789601048</v>
       </c>
       <c r="AJ10" t="n">
-        <v>71.02142857142857</v>
+        <v>1.069652801949182</v>
       </c>
       <c r="AK10" t="n">
-        <v>2107696.886446886</v>
+        <v>71.31638703804994</v>
       </c>
       <c r="AL10" t="n">
-        <v>72.99987789987789</v>
-      </c>
-      <c r="AM10" t="inlineStr">
+        <v>2857680.553483721</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>73.77954001127077</v>
+      </c>
+      <c r="AN10" t="inlineStr">
         <is>
           <t>IilCZTta</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>fmK213Ku</t>
         </is>
@@ -1930,84 +2008,85 @@
           <t>G8FL0ShI</t>
         </is>
       </c>
-      <c r="O11" t="n">
-        <v>26.67592592592592</v>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>186.2268518518518</v>
+        <v>26.22222222222222</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.643518518518519</v>
+        <v>185.1064814814815</v>
       </c>
       <c r="R11" t="n">
-        <v>76.4861111111111</v>
+        <v>1.518518518518519</v>
       </c>
       <c r="S11" t="n">
-        <v>10759259.25925926</v>
+        <v>75.62037037037037</v>
       </c>
       <c r="T11" t="n">
-        <v>79.33796296296296</v>
+        <v>9920833.333333334</v>
       </c>
       <c r="U11" t="n">
-        <v>28.02777777777778</v>
+        <v>78.84722222222223</v>
       </c>
       <c r="V11" t="n">
-        <v>180.0520833333333</v>
+        <v>28.65798611111111</v>
       </c>
       <c r="W11" t="n">
-        <v>2.366319444444445</v>
+        <v>179.828125</v>
       </c>
       <c r="X11" t="n">
-        <v>82.40972222222223</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="Y11" t="n">
-        <v>35282986.11111111</v>
+        <v>82.203125</v>
       </c>
       <c r="Z11" t="n">
-        <v>84.06597222222221</v>
+        <v>33149305.55555556</v>
       </c>
       <c r="AA11" t="n">
-        <v>28.78880702630703</v>
+        <v>83.67013888888889</v>
       </c>
       <c r="AB11" t="n">
-        <v>184.032683982684</v>
+        <v>27.91926645658264</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.782715201465201</v>
+        <v>183.1641104139024</v>
       </c>
       <c r="AD11" t="n">
-        <v>77.12527472527472</v>
+        <v>1.644544265074451</v>
       </c>
       <c r="AE11" t="n">
-        <v>9450986.045204796</v>
+        <v>76.55679571170573</v>
       </c>
       <c r="AF11" t="n">
-        <v>79.23274850149849</v>
+        <v>9335421.060694015</v>
       </c>
       <c r="AG11" t="n">
-        <v>26.05407196969697</v>
+        <v>79.17320622327878</v>
       </c>
       <c r="AH11" t="n">
-        <v>180.3499684343434</v>
+        <v>26.96886702049241</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.744176136363636</v>
+        <v>180.7552091011843</v>
       </c>
       <c r="AJ11" t="n">
-        <v>78.8046875</v>
+        <v>1.904880460956312</v>
       </c>
       <c r="AK11" t="n">
-        <v>22024498.10606061</v>
+        <v>78.70829709076612</v>
       </c>
       <c r="AL11" t="n">
-        <v>82.19138257575757</v>
-      </c>
-      <c r="AM11" t="inlineStr">
+        <v>20010981.16000786</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>81.61007420512064</v>
+      </c>
+      <c r="AN11" t="inlineStr">
         <is>
           <t>KWIuYKwG</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>AZ18LjKN</t>
         </is>
@@ -2063,84 +2142,89 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>26.36893939393939</v>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
       </c>
       <c r="P12" t="n">
-        <v>182.7083333333334</v>
+        <v>25.29382716049383</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.630934343434344</v>
+        <v>182.8719135802469</v>
       </c>
       <c r="R12" t="n">
-        <v>79.50416666666666</v>
+        <v>1.514814814814815</v>
       </c>
       <c r="S12" t="n">
-        <v>23455050.50505051</v>
+        <v>78.88672839506172</v>
       </c>
       <c r="T12" t="n">
-        <v>82.25265151515151</v>
+        <v>23387500</v>
       </c>
       <c r="U12" t="n">
-        <v>25.82407407407408</v>
+        <v>82.15833333333333</v>
       </c>
       <c r="V12" t="n">
-        <v>181.6296296296296</v>
+        <v>25.82291666666667</v>
       </c>
       <c r="W12" t="n">
-        <v>2.726851851851852</v>
+        <v>181.9045138888889</v>
       </c>
       <c r="X12" t="n">
-        <v>81.18055555555556</v>
+        <v>2.703125</v>
       </c>
       <c r="Y12" t="n">
-        <v>43268749.99999999</v>
+        <v>81.27951388888889</v>
       </c>
       <c r="Z12" t="n">
-        <v>85.69444444444446</v>
+        <v>44854861.1111111</v>
       </c>
       <c r="AA12" t="n">
-        <v>27.01436360627817</v>
+        <v>85.62326388888889</v>
       </c>
       <c r="AB12" t="n">
-        <v>182.0443326512739</v>
+        <v>25.26073692103104</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.497808430092946</v>
+        <v>181.7650546077017</v>
       </c>
       <c r="AD12" t="n">
-        <v>76.06315123557687</v>
+        <v>1.354055258467023</v>
       </c>
       <c r="AE12" t="n">
-        <v>12926339.73218069</v>
+        <v>75.40366975072858</v>
       </c>
       <c r="AF12" t="n">
-        <v>79.39481120272501</v>
+        <v>13228080.94955154</v>
       </c>
       <c r="AG12" t="n">
-        <v>23.63428493805816</v>
+        <v>79.78000311235606</v>
       </c>
       <c r="AH12" t="n">
-        <v>180.2672918788727</v>
+        <v>23.60959682638745</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.31785034388556</v>
+        <v>180.5017145857893</v>
       </c>
       <c r="AJ12" t="n">
-        <v>79.31517942304512</v>
+        <v>2.318392015116844</v>
       </c>
       <c r="AK12" t="n">
-        <v>38762751.66246722</v>
+        <v>79.44544067679081</v>
       </c>
       <c r="AL12" t="n">
-        <v>85.18902837251328</v>
-      </c>
-      <c r="AM12" t="inlineStr">
+        <v>40567152.92224303</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>85.261088863463</v>
+      </c>
+      <c r="AN12" t="inlineStr">
         <is>
           <t>0Q3vjDhH</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
@@ -2195,85 +2279,94 @@
           <t>super cup</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>25.83125</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
       </c>
       <c r="P13" t="n">
-        <v>182.39375</v>
+        <v>25.46157407407408</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.15</v>
+        <v>181.8776515151515</v>
       </c>
       <c r="R13" t="n">
-        <v>85.57499999999999</v>
+        <v>2.829040404040404</v>
       </c>
       <c r="S13" t="n">
-        <v>74753125</v>
+        <v>83.26292087542087</v>
       </c>
       <c r="T13" t="n">
-        <v>88.43125000000001</v>
+        <v>62781355.21885522</v>
       </c>
       <c r="U13" t="n">
-        <v>28.55787037037037</v>
+        <v>87.10732323232325</v>
       </c>
       <c r="V13" t="n">
-        <v>182.9606481481482</v>
+        <v>27.7020202020202</v>
       </c>
       <c r="W13" t="n">
-        <v>1.349537037037037</v>
+        <v>183.1858585858586</v>
       </c>
       <c r="X13" t="n">
-        <v>76.37037037037038</v>
+        <v>1.286868686868687</v>
       </c>
       <c r="Y13" t="n">
-        <v>10193981.48148148</v>
+        <v>75.77474747474747</v>
       </c>
       <c r="Z13" t="n">
-        <v>77.4375</v>
+        <v>9570101.010101011</v>
       </c>
       <c r="AA13" t="n">
-        <v>25.60019185643218</v>
+        <v>77.64444444444445</v>
       </c>
       <c r="AB13" t="n">
-        <v>180.8192107814786</v>
+        <v>25.10080790919606</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.912441507473435</v>
+        <v>180.1463379000385</v>
       </c>
       <c r="AD13" t="n">
-        <v>84.46844776203329</v>
+        <v>2.853098792654714</v>
       </c>
       <c r="AE13" t="n">
-        <v>66042421.27223697</v>
+        <v>83.29487480721033</v>
       </c>
       <c r="AF13" t="n">
-        <v>87.9041990109134</v>
+        <v>65050253.78952187</v>
       </c>
       <c r="AG13" t="n">
-        <v>27.50838874378157</v>
+        <v>87.42271092394448</v>
       </c>
       <c r="AH13" t="n">
-        <v>181.0505191759959</v>
+        <v>27.23065823065823</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.138691774084604</v>
+        <v>181.042402042402</v>
       </c>
       <c r="AJ13" t="n">
-        <v>74.95540890727771</v>
+        <v>1.114080364080364</v>
       </c>
       <c r="AK13" t="n">
-        <v>8302337.576117135</v>
+        <v>74.57303807303806</v>
       </c>
       <c r="AL13" t="n">
-        <v>76.77770971859452</v>
-      </c>
-      <c r="AM13" t="inlineStr">
+        <v>7789054.834054834</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>76.64912864912864</v>
+      </c>
+      <c r="AN13" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
         <is>
           <t>p2dFnNso</t>
         </is>
